--- a/Uno_CRM/public/templates/uno_import_template.xlsx
+++ b/Uno_CRM/public/templates/uno_import_template.xlsx
@@ -649,7 +649,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BVP01092026</v>
+        <v>BVP05072026</v>
       </c>
       <c r="B2" t="str">
         <v>PRJ-BVP1</v>
@@ -658,10 +658,10 @@
         <v>Budapest-Vienna-Prague</v>
       </c>
       <c r="D2" t="str">
-        <v>01.09.2026</v>
+        <v>05.07.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>07.09.2026</v>
+        <v>12.07.2026</v>
       </c>
       <c r="F2">
         <v>27</v>
@@ -718,13 +718,13 @@
         <v>Apex Travel Agency</v>
       </c>
       <c r="C2" t="str">
-        <v>Orta Avrupa 2026 Autumn Tours</v>
+        <v>Orta Avrupa 2026 Summer Tours</v>
       </c>
       <c r="D2" t="str">
-        <v>01.09.2026</v>
+        <v>01.07.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>30.09.2026</v>
+        <v>31.07.2026</v>
       </c>
       <c r="F2" t="str">
         <v>EUR</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BKG-01-BVP01092026</v>
+        <v>BKG-01-BVP05072026</v>
       </c>
       <c r="B2" t="str">
         <v>Ahmet</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>BKG-01-BVP01092026</v>
+        <v>BKG-01-BVP05072026</v>
       </c>
       <c r="B3" t="str">
         <v>Ayşe</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B4" t="str">
         <v>Mehmet</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B5" t="str">
         <v>Fatma</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B6" t="str">
         <v>Can</v>
